--- a/data/trans_dic/P37A$medicoedad-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoedad-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,17</t>
+          <t>0,22; 2,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,0</t>
+          <t>0,11; 1,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,39</t>
+          <t>0,14; 1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,59</t>
+          <t>0,52; 3,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,58</t>
+          <t>0,17; 1,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,98</t>
+          <t>0,15; 0,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,24</t>
+          <t>0,24; 1,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,9</t>
+          <t>0,36; 1,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,26</t>
+          <t>0,14; 1,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,98</t>
+          <t>0,14; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,83</t>
+          <t>0,25; 1,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,29</t>
+          <t>0,85; 2,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,82</t>
+          <t>0,09; 0,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,87</t>
+          <t>0,14; 0,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,89</t>
+          <t>0,15; 0,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,66</t>
+          <t>0,65; 1,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,46</t>
+          <t>1,09; 3,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,52</t>
+          <t>0,97; 3,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,8</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,54</t>
+          <t>1,12; 3,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,8</t>
+          <t>1,15; 2,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,81</t>
+          <t>0,09; 0,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,48</t>
+          <t>0,42; 1,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,99</t>
+          <t>1,25; 2,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,34</t>
+          <t>1,34; 2,69</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,37</t>
+          <t>4,07; 9,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,47</t>
+          <t>4,69; 9,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 10,63</t>
+          <t>5,42; 10,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,0</t>
+          <t>5,97; 10,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 9,0</t>
+          <t>4,21; 9,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 11,38</t>
+          <t>5,95; 11,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75; 11,11</t>
+          <t>5,94; 10,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 10,43</t>
+          <t>6,63; 10,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,89</t>
+          <t>4,65; 7,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,55</t>
+          <t>5,97; 9,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 9,71</t>
+          <t>6,25; 9,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 9,47</t>
+          <t>6,77; 9,36</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>46,52%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,08; 29,73</t>
+          <t>20,42; 30,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,58; 49,44</t>
+          <t>37,12; 49,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,65; 39,1</t>
+          <t>29,1; 40,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41,48; 49,8</t>
+          <t>40,58; 48,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,7; 36,76</t>
+          <t>27,32; 36,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,23; 35,96</t>
+          <t>26,25; 36,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,3; 35,88</t>
+          <t>26,07; 35,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,95; 83,93</t>
+          <t>44,62; 51,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,55; 32,33</t>
+          <t>25,59; 32,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,38; 41,2</t>
+          <t>32,97; 40,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,12; 36,3</t>
+          <t>28,73; 35,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,03; 78,18</t>
+          <t>43,77; 49,16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,27 +1524,27 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>53,94%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>54,35%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>52,04%</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>67,16%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>53,94%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>54,35%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>52,04%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>45,25; 58,37</t>
+          <t>44,99; 59,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,35; 60,13</t>
+          <t>47,1; 60,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,15; 60,33</t>
+          <t>49,29; 60,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63,11; 71,66</t>
+          <t>62,49; 71,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,33; 60,98</t>
+          <t>49,07; 60,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,29; 59,86</t>
+          <t>49,28; 59,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,72; 55,56</t>
+          <t>44,67; 55,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,74; 70,16</t>
+          <t>63,67; 70,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,3; 58,1</t>
+          <t>49,65; 58,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50,41; 58,65</t>
+          <t>50,05; 58,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48,16; 56,46</t>
+          <t>48,01; 56,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,44; 69,93</t>
+          <t>64,43; 69,73</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,13</t>
+          <t>5,55; 7,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 10,19</t>
+          <t>8,09; 10,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,04</t>
+          <t>8,18; 10,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,52; 13,71</t>
+          <t>12,18; 14,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,78; 10,77</t>
+          <t>8,7; 10,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,38; 11,44</t>
+          <t>9,4; 11,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,68; 11,97</t>
+          <t>9,63; 11,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,41; 34,86</t>
+          <t>15,25; 17,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,79</t>
+          <t>7,37; 8,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9,07; 10,53</t>
+          <t>9,1; 10,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,22; 10,71</t>
+          <t>9,22; 10,72</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,62; 23,79</t>
+          <t>14,03; 15,4</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>5064</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7527</t>
+          <t>0; 7823</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>984; 9834</t>
+          <t>995; 9924</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5499</t>
+          <t>0; 5315</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2098,32 +2098,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5132</t>
+          <t>0; 4615</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 18882</t>
+          <t>0; 16614</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6726</t>
+          <t>0; 7555</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>986; 8867</t>
+          <t>980; 9241</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6262</t>
+          <t>0; 6721</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 15770</t>
+          <t>0; 17231</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8555</t>
         </is>
       </c>
     </row>
@@ -2281,57 +2281,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>944; 9582</t>
+          <t>943; 9604</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8955</t>
+          <t>0; 9274</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2440; 15204</t>
+          <t>2459; 17118</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8525</t>
+          <t>0; 8499</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7217</t>
+          <t>0; 7289</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>877; 8910</t>
+          <t>978; 9358</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6099</t>
+          <t>0; 6473</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 8503</t>
+          <t>0; 8196</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2009; 12765</t>
+          <t>2000; 11925</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2659; 14293</t>
+          <t>2719; 13560</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3438; 17819</t>
+          <t>3522; 17473</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>13415</t>
         </is>
       </c>
     </row>
@@ -2489,57 +2489,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>949; 8600</t>
+          <t>933; 9252</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5609</t>
+          <t>0; 6105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>165; 10623</t>
+          <t>877; 9967</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1123; 10500</t>
+          <t>1123; 10487</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6796</t>
+          <t>0; 6902</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1252; 12126</t>
+          <t>1638; 11588</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4114; 13566</t>
+          <t>5279; 16421</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1134; 10880</t>
+          <t>1135; 9780</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1972; 12085</t>
+          <t>1894; 11291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1944; 11891</t>
+          <t>1933; 11939</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6068; 18711</t>
+          <t>8043; 22118</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25695</t>
+          <t>27176</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5036</t>
+          <t>0; 4117</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2050; 12463</t>
+          <t>2051; 12504</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6783; 22336</t>
+          <t>7054; 22401</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4088; 22406</t>
+          <t>6781; 21868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7719</t>
+          <t>0; 8073</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1141; 11098</t>
+          <t>1115; 10834</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7745; 22988</t>
+          <t>7284; 23118</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7854; 19987</t>
+          <t>8488; 20034</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>906; 8336</t>
+          <t>909; 8985</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4858; 18274</t>
+          <t>5200; 17869</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18197; 38672</t>
+          <t>16158; 37383</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13762; 37479</t>
+          <t>19243; 38716</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>47265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45906</t>
+          <t>50486</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89427</t>
+          <t>97751</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14436; 32375</t>
+          <t>15721; 35315</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19993; 40688</t>
+          <t>20122; 41297</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25689; 50783</t>
+          <t>25896; 50779</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33074; 56116</t>
+          <t>36397; 61731</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17324; 36365</t>
+          <t>17021; 36648</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26592; 50980</t>
+          <t>26630; 50254</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28577; 55185</t>
+          <t>29489; 54598</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36931; 57158</t>
+          <t>40385; 62384</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36182; 62379</t>
+          <t>36792; 62131</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51122; 83785</t>
+          <t>52374; 86169</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60852; 94675</t>
+          <t>60913; 96955</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>75232; 105090</t>
+          <t>82526; 114079</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168356</t>
+          <t>182382</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>398940</t>
+          <t>211321</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>567296</t>
+          <t>393703</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58744; 86976</t>
+          <t>59751; 88731</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>116406; 153160</t>
+          <t>115001; 153242</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95784; 130710</t>
+          <t>97274; 134263</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>152710; 183339</t>
+          <t>165195; 198431</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>94982; 126074</t>
+          <t>93681; 125879</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>92836; 127299</t>
+          <t>92918; 127422</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>99360; 135556</t>
+          <t>98497; 134967</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>285610; 510597</t>
+          <t>195948; 225703</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>162390; 205465</t>
+          <t>162626; 206335</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>221545; 273461</t>
+          <t>218873; 269338</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>207339; 258481</t>
+          <t>204598; 256282</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>449516; 763436</t>
+          <t>370419; 416027</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>190988</t>
+          <t>209354</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>285999</t>
+          <t>311035</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>476988</t>
+          <t>520388</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>94967; 122517</t>
+          <t>94429; 124120</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118293; 150235</t>
+          <t>117690; 149915</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>126326; 155035</t>
+          <t>126684; 156332</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>178442; 202625</t>
+          <t>193849; 222280</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>164705; 203605</t>
+          <t>163861; 202889</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>191736; 232862</t>
+          <t>191699; 233090</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>178975; 222320</t>
+          <t>178759; 223586</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>271409; 298779</t>
+          <t>295800; 325339</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>268089; 315970</t>
+          <t>270015; 318416</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>322044; 374694</t>
+          <t>319713; 373870</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>316459; 371040</t>
+          <t>315519; 368964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>456620; 495500</t>
+          <t>499205; 540257</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>425149</t>
+          <t>463037</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>758027</t>
+          <t>603015</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1183176</t>
+          <t>1066052</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>182065; 233678</t>
+          <t>181837; 233155</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>281299; 349296</t>
+          <t>277214; 352702</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>279868; 340765</t>
+          <t>277610; 344254</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>329445; 474346</t>
+          <t>430304; 497623</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>296561; 363853</t>
+          <t>294153; 367029</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>333750; 407204</t>
+          <t>334380; 408830</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>343255; 424348</t>
+          <t>341239; 423050</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>572244; 1294196</t>
+          <t>570051; 638987</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>494405; 585031</t>
+          <t>490841; 585437</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>633556; 735181</t>
+          <t>635343; 741090</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>639898; 743353</t>
+          <t>639817; 743952</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>976840; 1706409</t>
+          <t>1019898; 1119506</t>
         </is>
       </c>
     </row>
